--- a/data/Basic Functions and Conditional formatting task.xlsx
+++ b/data/Basic Functions and Conditional formatting task.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Assignments\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\kabir-sales-analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBF27CA-AADF-40B1-930D-4E977CF068F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794EB0B1-F7AC-4F57-BA55-0AEA94ACC65A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -125,7 +125,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -524,6 +524,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -545,19 +558,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -906,14 +906,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="24.6" x14ac:dyDescent="0.4">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -956,11 +956,11 @@
         <v>16720</v>
       </c>
       <c r="G3" s="5"/>
-      <c r="I3" s="27" t="s">
+      <c r="I3" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="28"/>
-      <c r="K3" s="29"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="36"/>
       <c r="N3" s="7"/>
       <c r="O3" s="8" t="s">
         <v>9</v>
@@ -1002,7 +1002,7 @@
       <c r="K4" s="23">
         <v>2012</v>
       </c>
-      <c r="N4" s="34" t="s">
+      <c r="N4" s="31" t="s">
         <v>12</v>
       </c>
       <c r="O4" s="13" t="s">
@@ -1036,7 +1036,7 @@
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
       <c r="K5" s="25"/>
-      <c r="N5" s="35"/>
+      <c r="N5" s="32"/>
       <c r="O5" s="13" t="s">
         <v>7</v>
       </c>
@@ -1068,7 +1068,7 @@
       <c r="I6" s="25"/>
       <c r="J6" s="25"/>
       <c r="K6" s="25"/>
-      <c r="N6" s="35"/>
+      <c r="N6" s="32"/>
       <c r="O6" s="13" t="s">
         <v>15</v>
       </c>
@@ -1100,7 +1100,7 @@
       <c r="I7" s="25"/>
       <c r="J7" s="25"/>
       <c r="K7" s="25"/>
-      <c r="N7" s="35"/>
+      <c r="N7" s="32"/>
       <c r="O7" s="13" t="s">
         <v>18</v>
       </c>
@@ -1132,7 +1132,7 @@
       <c r="I8" s="25"/>
       <c r="J8" s="25"/>
       <c r="K8" s="25"/>
-      <c r="N8" s="36"/>
+      <c r="N8" s="33"/>
       <c r="O8" s="17" t="s">
         <v>11</v>
       </c>
@@ -1269,11 +1269,11 @@
       <c r="F14" s="4">
         <v>10560</v>
       </c>
-      <c r="H14" s="31" t="s">
+      <c r="H14" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="32"/>
-      <c r="J14" s="33"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="40"/>
     </row>
     <row r="15" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
@@ -1312,11 +1312,11 @@
       <c r="O15" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="S15" s="27" t="s">
+      <c r="S15" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="T15" s="28"/>
-      <c r="U15" s="29"/>
+      <c r="T15" s="35"/>
+      <c r="U15" s="36"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="I16" s="13"/>
       <c r="J16" s="16"/>
-      <c r="L16" s="34" t="s">
+      <c r="L16" s="31" t="s">
         <v>23</v>
       </c>
       <c r="M16" s="13" t="s">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="I17" s="13"/>
       <c r="J17" s="16"/>
-      <c r="L17" s="35"/>
+      <c r="L17" s="32"/>
       <c r="M17" s="13" t="s">
         <v>7</v>
       </c>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="I18" s="13"/>
       <c r="J18" s="16"/>
-      <c r="L18" s="35"/>
+      <c r="L18" s="32"/>
       <c r="M18" s="13" t="s">
         <v>15</v>
       </c>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="I19" s="13"/>
       <c r="J19" s="16"/>
-      <c r="L19" s="35"/>
+      <c r="L19" s="32"/>
       <c r="M19" s="13" t="s">
         <v>18</v>
       </c>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="I20" s="13"/>
       <c r="J20" s="14"/>
-      <c r="L20" s="36"/>
+      <c r="L20" s="33"/>
       <c r="M20" s="17" t="s">
         <v>11</v>
       </c>
@@ -1655,19 +1655,19 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="S15:U15"/>
     <mergeCell ref="L16:L20"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="H14:J14"/>
     <mergeCell ref="N4:N8"/>
-    <mergeCell ref="S15:U15"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:F26">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>6000</formula>
+    </cfRule>
     <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>15000</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <formula>6000</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1685,14 +1685,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="24.6" x14ac:dyDescent="0.4">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1797,11 +1797,11 @@
       <c r="F6" s="4">
         <v>10560</v>
       </c>
-      <c r="K6" s="27" t="s">
+      <c r="K6" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="L6" s="28"/>
-      <c r="M6" s="29"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="36"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
@@ -1859,15 +1859,15 @@
       <c r="J8" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="37">
+      <c r="K8" s="27">
         <f>SUMIFS(E2:E26,D2:D26,"Abdul",C2:C26,2010)</f>
         <v>56</v>
       </c>
-      <c r="L8" s="37">
+      <c r="L8" s="27">
         <f>SUMIFS(E2:E26,D2:D26,"Abdul",C2:C26,2011)</f>
         <v>105</v>
       </c>
-      <c r="M8" s="37">
+      <c r="M8" s="27">
         <f>SUMIFS(E2:E26,D2:D26,"Abdul",C2:C26,2012)</f>
         <v>116</v>
       </c>
@@ -1895,15 +1895,15 @@
       <c r="J9" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="K9" s="37">
+      <c r="K9" s="27">
         <f>SUMIFS(E2:E26,D2:D26,"Ayo",C2:C26,2010)</f>
         <v>76</v>
       </c>
-      <c r="L9" s="37">
+      <c r="L9" s="27">
         <f>SUMIFS(E2:E26,D2:D26,"Ayo",C2:C26,2011)</f>
         <v>28</v>
       </c>
-      <c r="M9" s="37">
+      <c r="M9" s="27">
         <f>SUMIFS(E2:E26,D2:D26,"Ayo",C2:C26,2012)</f>
         <v>36</v>
       </c>
@@ -1931,15 +1931,15 @@
       <c r="J10" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="K10" s="37">
+      <c r="K10" s="27">
         <f>SUMIFS(E2:E26,D2:D26,"Ada",C2:C26,2010)</f>
         <v>122</v>
       </c>
-      <c r="L10" s="37">
+      <c r="L10" s="27">
         <f>SUMIFS(E2:E26,D2:D26,"Ada",C2:C26,2011)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="37">
+      <c r="M10" s="27">
         <f>SUMIFS(E2:E26,D2:D26,"Ada",C2:C26,2012)</f>
         <v>72</v>
       </c>
@@ -1967,15 +1967,15 @@
       <c r="J11" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="K11" s="37">
+      <c r="K11" s="27">
         <f>SUMIFS(E2:E26,D2:D26,"Ese",C2:C26,2010)</f>
         <v>90</v>
       </c>
-      <c r="L11" s="37">
+      <c r="L11" s="27">
         <f>SUMIFS(E2:E26,D2:D26,"Ese",C2:C26,2011)</f>
         <v>95</v>
       </c>
-      <c r="M11" s="37">
+      <c r="M11" s="27">
         <f>SUMIFS(E2:E26,D2:D26,"Ese",C2:C26,2012)</f>
         <v>52</v>
       </c>
@@ -2003,15 +2003,15 @@
       <c r="J12" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="K12" s="37">
+      <c r="K12" s="27">
         <f>SUMIFS(E2:E26,D2:D26,"Tola",C2:C26,2010)</f>
         <v>132</v>
       </c>
-      <c r="L12" s="37">
+      <c r="L12" s="27">
         <f>SUMIFS(E2:E26,D2:D26,"Tola",C2:C26,2011)</f>
         <v>152</v>
       </c>
-      <c r="M12" s="37">
+      <c r="M12" s="27">
         <f>SUMIFS(E2:E26,D2:D26,"Tola",C2:C26,2012)</f>
         <v>92</v>
       </c>
@@ -2332,14 +2332,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24.6" x14ac:dyDescent="0.4">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2381,7 +2381,7 @@
       <c r="F3" s="4">
         <v>16720</v>
       </c>
-      <c r="I3" s="38" t="s">
+      <c r="I3" s="28" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       <c r="F4" s="4">
         <v>12980</v>
       </c>
-      <c r="H4" s="40" t="s">
+      <c r="H4" s="30" t="s">
         <v>25</v>
       </c>
       <c r="I4" s="6" t="str">
@@ -2442,7 +2442,7 @@
         <v>12320</v>
       </c>
       <c r="H5" t="str">
-        <f t="shared" ref="H5:H9" si="1">D3</f>
+        <f t="shared" ref="H5:H8" si="1">D3</f>
         <v>Ayo</v>
       </c>
       <c r="I5">
@@ -2984,14 +2984,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24.6" x14ac:dyDescent="0.4">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -3159,11 +3159,11 @@
       <c r="F9" s="4">
         <v>5280</v>
       </c>
-      <c r="H9" s="31" t="s">
+      <c r="H9" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="32"/>
-      <c r="J9" s="33"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="40"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
@@ -3618,14 +3618,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24.6" x14ac:dyDescent="0.4">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
       <c r="H1" s="7"/>
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
@@ -3756,7 +3756,7 @@
         <v>8800</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -3797,6 +3797,7 @@
       <c r="F9" s="4">
         <v>5280</v>
       </c>
+      <c r="I9" s="7"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
@@ -3818,7 +3819,6 @@
       <c r="F10" s="4">
         <v>11000</v>
       </c>
-      <c r="I10" s="7"/>
       <c r="J10" s="8" t="s">
         <v>9</v>
       </c>
@@ -3849,7 +3849,7 @@
       <c r="F11" s="4">
         <v>7260</v>
       </c>
-      <c r="I11" s="34" t="s">
+      <c r="I11" s="31" t="s">
         <v>23</v>
       </c>
       <c r="J11" s="13" t="s">
@@ -3859,7 +3859,7 @@
         <f>SUMIF(D2:D26,"Abdul",E2:E26)</f>
         <v>277</v>
       </c>
-      <c r="L11" s="39">
+      <c r="L11" s="29">
         <f>SUMIF(D2:D27,"Abdul",F2:F27)</f>
         <v>60940</v>
       </c>
@@ -3884,7 +3884,7 @@
       <c r="F12" s="4">
         <v>20900</v>
       </c>
-      <c r="I12" s="35"/>
+      <c r="I12" s="32"/>
       <c r="J12" s="13" t="s">
         <v>7</v>
       </c>
@@ -3892,7 +3892,7 @@
         <f>SUMIF(D2:D26,"Ayo",E2:E26)</f>
         <v>140</v>
       </c>
-      <c r="L12" s="39">
+      <c r="L12" s="29">
         <f>SUMIF(D2:D27,"Ayo",F2:F27)</f>
         <v>30800</v>
       </c>
@@ -3917,7 +3917,7 @@
       <c r="F13" s="4">
         <v>12540</v>
       </c>
-      <c r="I13" s="35"/>
+      <c r="I13" s="32"/>
       <c r="J13" s="13" t="s">
         <v>15</v>
       </c>
@@ -3925,7 +3925,7 @@
         <f>SUMIF(D2:D26,"Ada",E2:E26)</f>
         <v>194</v>
       </c>
-      <c r="L13" s="39">
+      <c r="L13" s="29">
         <f>SUMIF(D2:D28,"Ada",F2:F28)</f>
         <v>42680</v>
       </c>
@@ -3950,7 +3950,7 @@
       <c r="F14" s="4">
         <v>10560</v>
       </c>
-      <c r="I14" s="35"/>
+      <c r="I14" s="32"/>
       <c r="J14" s="13" t="s">
         <v>18</v>
       </c>
@@ -3958,7 +3958,7 @@
         <f>SUMIF(D2:D26,"Ese",E2:E26)</f>
         <v>237</v>
       </c>
-      <c r="L14" s="39">
+      <c r="L14" s="29">
         <f>SUMIF(D2:D26,"Ese",F2:F26)</f>
         <v>52140</v>
       </c>
@@ -3983,7 +3983,7 @@
       <c r="F15" s="4">
         <v>19360</v>
       </c>
-      <c r="I15" s="36"/>
+      <c r="I15" s="33"/>
       <c r="J15" s="17" t="s">
         <v>11</v>
       </c>
@@ -3991,7 +3991,7 @@
         <f>SUMIF(D2:D26,"Tola",E2:E26)</f>
         <v>376</v>
       </c>
-      <c r="L15" s="39">
+      <c r="L15" s="29">
         <f>SUMIF(D2:D30,"Tola",F2:F30)</f>
         <v>82720</v>
       </c>
@@ -4249,14 +4249,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24.6" x14ac:dyDescent="0.4">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -4410,7 +4410,7 @@
       <c r="F8" s="4">
         <v>19800</v>
       </c>
-      <c r="J8" s="34" t="s">
+      <c r="J8" s="31" t="s">
         <v>12</v>
       </c>
       <c r="K8" s="13" t="s">
@@ -4441,7 +4441,7 @@
       <c r="F9" s="4">
         <v>5280</v>
       </c>
-      <c r="J9" s="35"/>
+      <c r="J9" s="32"/>
       <c r="K9" s="13" t="s">
         <v>7</v>
       </c>
@@ -4470,7 +4470,7 @@
       <c r="F10" s="4">
         <v>11000</v>
       </c>
-      <c r="J10" s="35"/>
+      <c r="J10" s="32"/>
       <c r="K10" s="13" t="s">
         <v>15</v>
       </c>
@@ -4499,7 +4499,7 @@
       <c r="F11" s="4">
         <v>7260</v>
       </c>
-      <c r="J11" s="35"/>
+      <c r="J11" s="32"/>
       <c r="K11" s="13" t="s">
         <v>18</v>
       </c>
@@ -4528,7 +4528,7 @@
       <c r="F12" s="4">
         <v>20900</v>
       </c>
-      <c r="J12" s="36"/>
+      <c r="J12" s="33"/>
       <c r="K12" s="17" t="s">
         <v>11</v>
       </c>
